--- a/jira_export_2026-06-24.xlsx
+++ b/jira_export_2026-06-24.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>622 h</t>
+          <t>623 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P189"/>
+  <dimension ref="A1:P192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -13040,18 +13040,18 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr"/>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr"/>
@@ -13068,11 +13068,11 @@
       <c r="H177" s="12" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" s="12" t="n">
         <v>0.25</v>
@@ -13092,18 +13092,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1278</t>
+          <t>PSC-1294</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13120,14 +13120,14 @@
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L178" s="15" t="inlineStr"/>
       <c r="M178" s="15" t="inlineStr"/>
@@ -13144,18 +13144,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13166,35 +13166,27 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M179" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr"/>
+      <c r="M179" s="12" t="inlineStr"/>
       <c r="N179" s="13" t="n">
-        <v>1191.4</v>
-      </c>
-      <c r="O179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P179" s="13" t="n">
@@ -13204,18 +13196,18 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr"/>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr"/>
@@ -13232,7 +13224,7 @@
       <c r="H180" s="15" t="inlineStr"/>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
@@ -13256,18 +13248,18 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PSC-1257</t>
+          <t>PSC-1278</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr"/>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -13284,14 +13276,14 @@
       <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L181" s="12" t="inlineStr"/>
       <c r="M181" s="12" t="inlineStr"/>
@@ -13308,18 +13300,18 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PSC-1252</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr"/>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr"/>
@@ -13330,27 +13322,35 @@
       </c>
       <c r="G182" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H182" s="15" t="inlineStr"/>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L182" s="15" t="inlineStr"/>
-      <c r="M182" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L182" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M182" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N182" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" s="16" t="n">
+        <v>1191.4</v>
+      </c>
+      <c r="O182" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P182" s="16" t="n">
@@ -13360,18 +13360,18 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-1245</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr"/>
@@ -13388,11 +13388,11 @@
       <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K183" s="12" t="n">
         <v>0.25</v>
@@ -13412,18 +13412,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1257</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13434,56 +13434,48 @@
       </c>
       <c r="G184" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K184" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L184" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33167</t>
-        </is>
-      </c>
-      <c r="M184" s="15" t="inlineStr">
-        <is>
-          <t>00165437</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L184" s="15" t="inlineStr"/>
+      <c r="M184" s="15" t="inlineStr"/>
       <c r="N184" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O184" s="17" t="n">
-        <v>250</v>
+        <v>0</v>
+      </c>
+      <c r="O184" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P184" s="16" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1252</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13494,13 +13486,13 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
@@ -13509,41 +13501,33 @@
       <c r="K185" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="L185" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32829</t>
-        </is>
-      </c>
-      <c r="M185" s="12" t="inlineStr">
-        <is>
-          <t>00163534</t>
-        </is>
-      </c>
+      <c r="L185" s="12" t="inlineStr"/>
+      <c r="M185" s="12" t="inlineStr"/>
       <c r="N185" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O185" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P185" s="13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1245</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13560,14 +13544,14 @@
       <c r="H186" s="15" t="inlineStr"/>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="J186" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L186" s="15" t="inlineStr"/>
       <c r="M186" s="15" t="inlineStr"/>
@@ -13584,18 +13568,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1147</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13606,46 +13590,58 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L187" s="12" t="inlineStr"/>
-      <c r="M187" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L187" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33167</t>
+        </is>
+      </c>
+      <c r="M187" s="12" t="inlineStr">
+        <is>
+          <t>00165437</t>
+        </is>
+      </c>
       <c r="N187" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O187" s="13" t="n">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="O187" s="17" t="n">
+        <v>250</v>
       </c>
       <c r="P187" s="13" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1145</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOLBEC</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
-      <c r="D188" s="15" t="inlineStr"/>
+      <c r="D188" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
       <c r="E188" s="15" t="inlineStr"/>
       <c r="F188" s="15" t="inlineStr">
         <is>
@@ -13660,61 +13656,221 @@
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="J188" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L188" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M188" s="15" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
+      <c r="N188" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="O188" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="P188" s="16" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1182</t>
+        </is>
+      </c>
+      <c r="B189" s="12" t="inlineStr">
+        <is>
+          <t>Commune de La Ville aux Dames</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr"/>
+      <c r="D189" s="12" t="inlineStr">
+        <is>
+          <t>Commune de La Ville aux Dames</t>
+        </is>
+      </c>
+      <c r="E189" s="12" t="inlineStr"/>
+      <c r="F189" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G189" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H189" s="12" t="inlineStr"/>
+      <c r="I189" s="12" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="J189" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L189" s="12" t="inlineStr"/>
+      <c r="M189" s="12" t="inlineStr"/>
+      <c r="N189" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1147</t>
+        </is>
+      </c>
+      <c r="B190" s="15" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
+      <c r="C190" s="15" t="inlineStr"/>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
+      <c r="E190" s="15" t="inlineStr"/>
+      <c r="F190" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G190" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H190" s="15" t="inlineStr"/>
+      <c r="I190" s="15" t="inlineStr">
+        <is>
           <t>12/02/2026</t>
         </is>
       </c>
-      <c r="J188" s="15" t="n">
+      <c r="J190" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K188" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" s="15" t="inlineStr">
+      <c r="K190" s="15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L190" s="15" t="inlineStr"/>
+      <c r="M190" s="15" t="inlineStr"/>
+      <c r="N190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1145</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BOLBEC</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr"/>
+      <c r="D191" s="12" t="inlineStr"/>
+      <c r="E191" s="12" t="inlineStr"/>
+      <c r="F191" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H191" s="12" t="inlineStr"/>
+      <c r="I191" s="12" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="J191" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K191" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-31452</t>
         </is>
       </c>
-      <c r="M188" s="15" t="inlineStr">
+      <c r="M191" s="12" t="inlineStr">
         <is>
           <t>00156409</t>
         </is>
       </c>
-      <c r="N188" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" s="16" t="n">
+      <c r="N191" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="P188" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="18" t="inlineStr">
+      <c r="P191" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B189" s="18" t="inlineStr"/>
-      <c r="C189" s="18" t="inlineStr"/>
-      <c r="D189" s="18" t="inlineStr"/>
-      <c r="E189" s="18" t="inlineStr"/>
-      <c r="F189" s="18" t="inlineStr"/>
-      <c r="G189" s="18" t="inlineStr"/>
-      <c r="H189" s="18" t="inlineStr"/>
-      <c r="I189" s="18" t="inlineStr"/>
-      <c r="J189" s="18" t="inlineStr"/>
-      <c r="K189" s="18" t="inlineStr"/>
-      <c r="L189" s="18" t="inlineStr"/>
-      <c r="M189" s="18" t="inlineStr"/>
-      <c r="N189" s="19" t="n">
+      <c r="B192" s="18" t="inlineStr"/>
+      <c r="C192" s="18" t="inlineStr"/>
+      <c r="D192" s="18" t="inlineStr"/>
+      <c r="E192" s="18" t="inlineStr"/>
+      <c r="F192" s="18" t="inlineStr"/>
+      <c r="G192" s="18" t="inlineStr"/>
+      <c r="H192" s="18" t="inlineStr"/>
+      <c r="I192" s="18" t="inlineStr"/>
+      <c r="J192" s="18" t="inlineStr"/>
+      <c r="K192" s="18" t="inlineStr"/>
+      <c r="L192" s="18" t="inlineStr"/>
+      <c r="M192" s="18" t="inlineStr"/>
+      <c r="N192" s="19" t="n">
         <v>69796.84</v>
       </c>
-      <c r="O189" s="19" t="n">
+      <c r="O192" s="19" t="n">
         <v>46331.85</v>
       </c>
-      <c r="P189" s="19" t="n">
-        <v>116.85</v>
+      <c r="P192" s="19" t="n">
+        <v>116.63</v>
       </c>
     </row>
   </sheetData>
@@ -13904,6 +14060,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15091,10 +15250,10 @@
         <v>43</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>275.5</v>
+        <v>276.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>80</v>
@@ -15104,7 +15263,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-06-24.xlsx
+++ b/jira_export_2026-06-24.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>623 h</t>
+          <t>624 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P192"/>
+  <dimension ref="A1:P193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL PASTELL + DA DPA</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -13040,18 +13040,18 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr"/>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr"/>
@@ -13068,7 +13068,7 @@
       <c r="H177" s="12" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
@@ -13092,18 +13092,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1294</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13120,7 +13120,7 @@
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
@@ -13144,18 +13144,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1294</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13196,18 +13196,18 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr"/>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr"/>
@@ -13224,11 +13224,11 @@
       <c r="H180" s="15" t="inlineStr"/>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="15" t="n">
         <v>0.25</v>
@@ -13248,18 +13248,18 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PSC-1278</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr"/>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -13276,14 +13276,14 @@
       <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L181" s="12" t="inlineStr"/>
       <c r="M181" s="12" t="inlineStr"/>
@@ -13300,18 +13300,18 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1278</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr"/>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr"/>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="G182" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H182" s="15" t="inlineStr"/>
@@ -13335,22 +13335,14 @@
         <v>1</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M182" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L182" s="15" t="inlineStr"/>
+      <c r="M182" s="15" t="inlineStr"/>
       <c r="N182" s="16" t="n">
-        <v>1191.4</v>
-      </c>
-      <c r="O182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P182" s="16" t="n">
@@ -13360,18 +13352,18 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr"/>
@@ -13382,27 +13374,35 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L183" s="12" t="inlineStr"/>
-      <c r="M183" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L183" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M183" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N183" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" s="13" t="n">
+        <v>1191.4</v>
+      </c>
+      <c r="O183" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P183" s="13" t="n">
@@ -13412,18 +13412,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1257</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13440,14 +13440,14 @@
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L184" s="15" t="inlineStr"/>
       <c r="M184" s="15" t="inlineStr"/>
@@ -13464,18 +13464,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1252</t>
+          <t>PSC-1257</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13492,14 +13492,14 @@
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L185" s="12" t="inlineStr"/>
       <c r="M185" s="12" t="inlineStr"/>
@@ -13516,18 +13516,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1245</t>
+          <t>PSC-1252</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13568,18 +13568,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1245</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13590,56 +13590,48 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L187" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33167</t>
-        </is>
-      </c>
-      <c r="M187" s="12" t="inlineStr">
-        <is>
-          <t>00165437</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L187" s="12" t="inlineStr"/>
+      <c r="M187" s="12" t="inlineStr"/>
       <c r="N187" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="O187" s="17" t="n">
-        <v>250</v>
+        <v>0</v>
+      </c>
+      <c r="O187" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P187" s="13" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13656,50 +13648,50 @@
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J188" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L188" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32829</t>
+          <t>PDMDEP-33167</t>
         </is>
       </c>
       <c r="M188" s="15" t="inlineStr">
         <is>
-          <t>00163534</t>
+          <t>00165437</t>
         </is>
       </c>
       <c r="N188" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="O188" s="16" t="n">
-        <v>50</v>
+        <v>500</v>
+      </c>
+      <c r="O188" s="17" t="n">
+        <v>250</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13710,48 +13702,56 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J189" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L189" s="12" t="inlineStr"/>
-      <c r="M189" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L189" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M189" s="12" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N189" s="13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O189" s="13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P189" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1147</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13768,14 +13768,14 @@
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L190" s="15" t="inlineStr"/>
       <c r="M190" s="15" t="inlineStr"/>
@@ -13792,16 +13792,20 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-1145</t>
+          <t>PSC-1147</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOLBEC</t>
+          <t>Commune de COUTANCES</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
-      <c r="D191" s="12" t="inlineStr"/>
+      <c r="D191" s="12" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
       <c r="E191" s="12" t="inlineStr"/>
       <c r="F191" s="12" t="inlineStr">
         <is>
@@ -13810,7 +13814,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr"/>
@@ -13823,54 +13827,102 @@
         <v>4</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" s="12" t="inlineStr">
+        <v>1.25</v>
+      </c>
+      <c r="L191" s="12" t="inlineStr"/>
+      <c r="M191" s="12" t="inlineStr"/>
+      <c r="N191" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1145</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BOLBEC</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr"/>
+      <c r="D192" s="15" t="inlineStr"/>
+      <c r="E192" s="15" t="inlineStr"/>
+      <c r="F192" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G192" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H192" s="15" t="inlineStr"/>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="J192" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K192" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-31452</t>
         </is>
       </c>
-      <c r="M191" s="12" t="inlineStr">
+      <c r="M192" s="15" t="inlineStr">
         <is>
           <t>00156409</t>
         </is>
       </c>
-      <c r="N191" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O191" s="13" t="n">
+      <c r="N192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="P191" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="18" t="inlineStr">
+      <c r="P192" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B192" s="18" t="inlineStr"/>
-      <c r="C192" s="18" t="inlineStr"/>
-      <c r="D192" s="18" t="inlineStr"/>
-      <c r="E192" s="18" t="inlineStr"/>
-      <c r="F192" s="18" t="inlineStr"/>
-      <c r="G192" s="18" t="inlineStr"/>
-      <c r="H192" s="18" t="inlineStr"/>
-      <c r="I192" s="18" t="inlineStr"/>
-      <c r="J192" s="18" t="inlineStr"/>
-      <c r="K192" s="18" t="inlineStr"/>
-      <c r="L192" s="18" t="inlineStr"/>
-      <c r="M192" s="18" t="inlineStr"/>
-      <c r="N192" s="19" t="n">
+      <c r="B193" s="18" t="inlineStr"/>
+      <c r="C193" s="18" t="inlineStr"/>
+      <c r="D193" s="18" t="inlineStr"/>
+      <c r="E193" s="18" t="inlineStr"/>
+      <c r="F193" s="18" t="inlineStr"/>
+      <c r="G193" s="18" t="inlineStr"/>
+      <c r="H193" s="18" t="inlineStr"/>
+      <c r="I193" s="18" t="inlineStr"/>
+      <c r="J193" s="18" t="inlineStr"/>
+      <c r="K193" s="18" t="inlineStr"/>
+      <c r="L193" s="18" t="inlineStr"/>
+      <c r="M193" s="18" t="inlineStr"/>
+      <c r="N193" s="19" t="n">
         <v>69796.84</v>
       </c>
-      <c r="O192" s="19" t="n">
+      <c r="O193" s="19" t="n">
         <v>46331.85</v>
       </c>
-      <c r="P192" s="19" t="n">
-        <v>116.63</v>
+      <c r="P193" s="19" t="n">
+        <v>116.56</v>
       </c>
     </row>
   </sheetData>
@@ -14063,6 +14115,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15250,10 +15303,10 @@
         <v>43</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>276.25</v>
+        <v>276.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>80</v>
@@ -15263,7 +15316,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-06-24.xlsx
+++ b/jira_export_2026-06-24.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>624 h</t>
+          <t>633 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P193"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4233,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>675</v>
       </c>
       <c r="P49" s="13" t="n">
-        <v>225</v>
+        <v>207.69</v>
       </c>
     </row>
     <row r="50">
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>320</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>106.67</v>
+        <v>98.45999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -5793,7 +5793,7 @@
         <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>4.75</v>
+        <v>7.75</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>1228.5</v>
       </c>
       <c r="P71" s="13" t="n">
-        <v>258.63</v>
+        <v>158.52</v>
       </c>
     </row>
     <row r="72">
@@ -10127,7 +10127,7 @@
         <v>10</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
@@ -11520,22 +11520,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -11565,7 +11565,7 @@
         <v>18</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>11.75</v>
+        <v>0.25</v>
       </c>
       <c r="L153" s="12" t="inlineStr"/>
       <c r="M153" s="12" t="inlineStr"/>
@@ -11582,12 +11582,12 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11610,40 +11610,32 @@
       </c>
       <c r="G154" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
         <v>18</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M154" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>11.75</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr"/>
+      <c r="M154" s="15" t="inlineStr"/>
       <c r="N154" s="16" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="O154" s="16" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="P154" s="16" t="n">
         <v>0</v>
@@ -11652,22 +11644,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11675,7 +11667,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -11685,35 +11677,35 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N155" s="13" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="O155" s="13" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="P155" s="13" t="n">
         <v>0</v>
@@ -11722,12 +11714,12 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
@@ -11737,7 +11729,7 @@
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11767,16 +11759,16 @@
         <v>18</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M156" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N156" s="16" t="n">
@@ -11792,12 +11784,12 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-17594</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[CD 40 LANDES] Param Interfaces + dev spé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -11807,7 +11799,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>CD 40</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11830,30 +11822,30 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28016</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>453168</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N157" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O157" s="13" t="n">
-        <v>239.25</v>
+        <v>0</v>
       </c>
       <c r="P157" s="13" t="n">
         <v>0</v>
@@ -11862,12 +11854,12 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-17291</t>
+          <t>PDMDEP-17594</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[EVREUX] Littéralis Expert</t>
+          <t>[CD 40 LANDES] Param Interfaces + dev spé</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
@@ -11877,7 +11869,7 @@
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>CD 40</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11895,35 +11887,35 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>29/10/2024</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K158" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27496</t>
+          <t>PDMDEP-28016</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
         <is>
-          <t>450556</t>
+          <t>453168</t>
         </is>
       </c>
       <c r="N158" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O158" s="16" t="n">
-        <v>1650</v>
+        <v>239.25</v>
       </c>
       <c r="P158" s="16" t="n">
         <v>0</v>
@@ -11932,22 +11924,22 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-17291</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[EVREUX] Littéralis Expert</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -11955,37 +11947,45 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L159" s="12" t="inlineStr"/>
-      <c r="M159" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L159" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27496</t>
+        </is>
+      </c>
+      <c r="M159" s="12" t="inlineStr">
+        <is>
+          <t>450556</t>
+        </is>
+      </c>
       <c r="N159" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O159" s="13" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="P159" s="13" t="n">
         <v>0</v>
@@ -11994,22 +11994,22 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16116</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G160" s="15" t="inlineStr">
@@ -12027,19 +12027,19 @@
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L160" s="15" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -12056,22 +12056,22 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12094,14 +12094,14 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L161" s="12" t="inlineStr"/>
       <c r="M161" s="12" t="inlineStr"/>
@@ -12118,22 +12118,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12156,14 +12156,14 @@
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12180,22 +12180,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12213,19 +12213,19 @@
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -12242,22 +12242,22 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12275,19 +12275,19 @@
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L164" s="15" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -12304,12 +12304,12 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12337,19 +12337,19 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
         <v>31</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L165" s="12" t="inlineStr"/>
       <c r="M165" s="12" t="inlineStr"/>
@@ -12366,22 +12366,22 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12404,14 +12404,14 @@
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12428,22 +12428,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12456,35 +12456,27 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="L167" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M167" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L167" s="12" t="inlineStr"/>
+      <c r="M167" s="12" t="inlineStr"/>
       <c r="N167" s="13" t="n">
         <v>0</v>
       </c>
@@ -12498,22 +12490,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12529,20 +12521,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H168" s="15" t="inlineStr"/>
+      <c r="H168" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L168" s="15" t="inlineStr"/>
-      <c r="M168" s="15" t="inlineStr"/>
+        <v>10.25</v>
+      </c>
+      <c r="L168" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M168" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N168" s="16" t="n">
         <v>0</v>
       </c>
@@ -12556,12 +12560,12 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
@@ -12571,7 +12575,7 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12584,24 +12588,20 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H169" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr"/>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
       <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
@@ -12618,12 +12618,12 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12656,14 +12656,14 @@
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>10.75</v>
+        <v>3.5</v>
       </c>
       <c r="L170" s="15" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -12680,28 +12680,26 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v/>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
@@ -12727,7 +12725,7 @@
         <v>33</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0.5</v>
+        <v>10.75</v>
       </c>
       <c r="L171" s="12" t="inlineStr"/>
       <c r="M171" s="12" t="inlineStr"/>
@@ -12744,12 +12742,12 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
@@ -12759,12 +12757,12 @@
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F172" s="15" t="inlineStr">
@@ -12779,7 +12777,7 @@
       </c>
       <c r="H172" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I172" s="15" t="inlineStr">
@@ -12791,7 +12789,7 @@
         <v>33</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -12808,23 +12806,27 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C173" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
@@ -12839,19 +12841,19 @@
       </c>
       <c r="H173" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="L173" s="12" t="inlineStr"/>
       <c r="M173" s="12" t="inlineStr"/>
@@ -12868,36 +12870,50 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-4703</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>[Amelie Les Bains Palalda - Placier v2 + Paiement CB] GEODP V2</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr"/>
-      <c r="D174" s="15" t="inlineStr"/>
-      <c r="E174" s="15" t="n">
-        <v/>
+      <c r="D174" s="15" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E174" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F174" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G174" s="15" t="inlineStr"/>
-      <c r="H174" s="15" t="inlineStr"/>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G174" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H174" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>02/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -12914,52 +12930,36 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-4137</t>
+          <t>PDMDEP-4703</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>[NIORT] LITTERALIS PRIME</t>
-        </is>
-      </c>
-      <c r="C175" s="12" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D175" s="12" t="inlineStr">
-        <is>
-          <t>COMMUNE DE NIORT</t>
-        </is>
-      </c>
+          <t>[Amelie Les Bains Palalda - Placier v2 + Paiement CB] GEODP V2</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr"/>
+      <c r="D175" s="12" t="inlineStr"/>
       <c r="E175" s="12" t="n">
         <v/>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G175" s="12" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H175" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G175" s="12" t="inlineStr"/>
+      <c r="H175" s="12" t="inlineStr"/>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>27/08/2023</t>
+          <t>02/09/2023</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -12976,12 +12976,12 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-4137</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[NIORT] LITTERALIS PRIME</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr">
@@ -12991,13 +12991,11 @@
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E176" s="15" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
+          <t>COMMUNE DE NIORT</t>
+        </is>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v/>
       </c>
       <c r="F176" s="15" t="inlineStr">
         <is>
@@ -13011,12 +13009,12 @@
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>27/08/2023</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
@@ -13040,21 +13038,29 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
-        </is>
-      </c>
-      <c r="C177" s="12" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
-        </is>
-      </c>
-      <c r="E177" s="12" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13062,20 +13068,24 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H177" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H177" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L177" s="12" t="inlineStr"/>
       <c r="M177" s="12" t="inlineStr"/>
@@ -13092,18 +13102,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13120,7 +13130,7 @@
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
@@ -13144,18 +13154,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-1294</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13172,7 +13182,7 @@
       <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
@@ -13196,18 +13206,18 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1294</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr"/>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr"/>
@@ -13248,18 +13258,18 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr"/>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -13276,11 +13286,11 @@
       <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" s="12" t="n">
         <v>0.25</v>
@@ -13300,18 +13310,18 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PSC-1278</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr"/>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr"/>
@@ -13328,14 +13338,14 @@
       <c r="H182" s="15" t="inlineStr"/>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L182" s="15" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -13352,18 +13362,18 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1278</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr"/>
@@ -13374,7 +13384,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr"/>
@@ -13387,22 +13397,14 @@
         <v>1</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M183" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L183" s="12" t="inlineStr"/>
+      <c r="M183" s="12" t="inlineStr"/>
       <c r="N183" s="13" t="n">
-        <v>1191.4</v>
-      </c>
-      <c r="O183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P183" s="13" t="n">
@@ -13412,18 +13414,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13434,27 +13436,35 @@
       </c>
       <c r="G184" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L184" s="15" t="inlineStr"/>
-      <c r="M184" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L184" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M184" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N184" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O184" s="16" t="n">
+        <v>1191.4</v>
+      </c>
+      <c r="O184" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P184" s="16" t="n">
@@ -13464,18 +13474,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1257</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13492,14 +13502,14 @@
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L185" s="12" t="inlineStr"/>
       <c r="M185" s="12" t="inlineStr"/>
@@ -13516,18 +13526,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1252</t>
+          <t>PSC-1257</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13544,14 +13554,14 @@
       <c r="H186" s="15" t="inlineStr"/>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J186" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L186" s="15" t="inlineStr"/>
       <c r="M186" s="15" t="inlineStr"/>
@@ -13568,18 +13578,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1245</t>
+          <t>PSC-1252</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13620,18 +13630,18 @@
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1245</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13642,56 +13652,48 @@
       </c>
       <c r="G188" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="J188" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L188" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33167</t>
-        </is>
-      </c>
-      <c r="M188" s="15" t="inlineStr">
-        <is>
-          <t>00165437</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L188" s="15" t="inlineStr"/>
+      <c r="M188" s="15" t="inlineStr"/>
       <c r="N188" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O188" s="17" t="n">
-        <v>250</v>
+        <v>0</v>
+      </c>
+      <c r="O188" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13708,50 +13710,50 @@
       <c r="H189" s="12" t="inlineStr"/>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J189" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L189" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32829</t>
+          <t>PDMDEP-33167</t>
         </is>
       </c>
       <c r="M189" s="12" t="inlineStr">
         <is>
-          <t>00163534</t>
+          <t>00165437</t>
         </is>
       </c>
       <c r="N189" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O189" s="13" t="n">
-        <v>50</v>
+        <v>500</v>
+      </c>
+      <c r="O189" s="17" t="n">
+        <v>250</v>
       </c>
       <c r="P189" s="13" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13762,48 +13764,56 @@
       </c>
       <c r="G190" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L190" s="15" t="inlineStr"/>
-      <c r="M190" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L190" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M190" s="15" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N190" s="16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O190" s="16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P190" s="16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-1147</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -13820,14 +13830,14 @@
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J191" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L191" s="12" t="inlineStr"/>
       <c r="M191" s="12" t="inlineStr"/>
@@ -13844,16 +13854,20 @@
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>PSC-1145</t>
+          <t>PSC-1147</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOLBEC</t>
+          <t>Commune de COUTANCES</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr"/>
-      <c r="D192" s="15" t="inlineStr"/>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
       <c r="E192" s="15" t="inlineStr"/>
       <c r="F192" s="15" t="inlineStr">
         <is>
@@ -13862,7 +13876,7 @@
       </c>
       <c r="G192" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H192" s="15" t="inlineStr"/>
@@ -13875,54 +13889,102 @@
         <v>4</v>
       </c>
       <c r="K192" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" s="15" t="inlineStr">
+        <v>1.25</v>
+      </c>
+      <c r="L192" s="15" t="inlineStr"/>
+      <c r="M192" s="15" t="inlineStr"/>
+      <c r="N192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1145</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BOLBEC</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr"/>
+      <c r="D193" s="12" t="inlineStr"/>
+      <c r="E193" s="12" t="inlineStr"/>
+      <c r="F193" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H193" s="12" t="inlineStr"/>
+      <c r="I193" s="12" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="J193" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K193" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-31452</t>
         </is>
       </c>
-      <c r="M192" s="15" t="inlineStr">
+      <c r="M193" s="12" t="inlineStr">
         <is>
           <t>00156409</t>
         </is>
       </c>
-      <c r="N192" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" s="16" t="n">
+      <c r="N193" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="P192" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="18" t="inlineStr">
+      <c r="P193" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B193" s="18" t="inlineStr"/>
-      <c r="C193" s="18" t="inlineStr"/>
-      <c r="D193" s="18" t="inlineStr"/>
-      <c r="E193" s="18" t="inlineStr"/>
-      <c r="F193" s="18" t="inlineStr"/>
-      <c r="G193" s="18" t="inlineStr"/>
-      <c r="H193" s="18" t="inlineStr"/>
-      <c r="I193" s="18" t="inlineStr"/>
-      <c r="J193" s="18" t="inlineStr"/>
-      <c r="K193" s="18" t="inlineStr"/>
-      <c r="L193" s="18" t="inlineStr"/>
-      <c r="M193" s="18" t="inlineStr"/>
-      <c r="N193" s="19" t="n">
+      <c r="B194" s="18" t="inlineStr"/>
+      <c r="C194" s="18" t="inlineStr"/>
+      <c r="D194" s="18" t="inlineStr"/>
+      <c r="E194" s="18" t="inlineStr"/>
+      <c r="F194" s="18" t="inlineStr"/>
+      <c r="G194" s="18" t="inlineStr"/>
+      <c r="H194" s="18" t="inlineStr"/>
+      <c r="I194" s="18" t="inlineStr"/>
+      <c r="J194" s="18" t="inlineStr"/>
+      <c r="K194" s="18" t="inlineStr"/>
+      <c r="L194" s="18" t="inlineStr"/>
+      <c r="M194" s="18" t="inlineStr"/>
+      <c r="N194" s="19" t="n">
         <v>69796.84</v>
       </c>
-      <c r="O193" s="19" t="n">
+      <c r="O194" s="19" t="n">
         <v>46331.85</v>
       </c>
-      <c r="P193" s="19" t="n">
-        <v>116.56</v>
+      <c r="P194" s="19" t="n">
+        <v>114.04</v>
       </c>
     </row>
   </sheetData>
@@ -14116,6 +14178,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15297,16 +15360,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>222.5</v>
+        <v>230.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>11</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>276.5</v>
+        <v>285.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>80</v>
@@ -15316,7 +15379,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15421,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>126</v>
+        <v>126.75</v>
       </c>
     </row>
   </sheetData>
@@ -15446,13 +15509,13 @@
         <v>376431</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>173034</v>
+        <v>174757</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>203397</v>
+        <v>201674</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>164581</v>
+        <v>162858</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>18605</v>
@@ -15471,13 +15534,13 @@
         <v>197304</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>92755</v>
+        <v>90555</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>104549</v>
+        <v>106749</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>95630</v>
+        <v>97830</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>4070</v>
@@ -15496,13 +15559,13 @@
         <v>179127</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>80279</v>
+        <v>84202</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>98848</v>
+        <v>94925</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>68951</v>
+        <v>65028</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>14535</v>

--- a/jira_export_2026-06-24.xlsx
+++ b/jira_export_2026-06-24.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>633 h</t>
+          <t>652 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>4</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>967.05</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>128.94</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -8449,7 +8449,7 @@
         <v>6</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.25</v>
+        <v>3.25</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>18</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L153" s="12" t="inlineStr"/>
       <c r="M153" s="12" t="inlineStr"/>
@@ -13984,7 +13984,7 @@
         <v>46331.85</v>
       </c>
       <c r="P194" s="19" t="n">
-        <v>114.04</v>
+        <v>111.57</v>
       </c>
     </row>
   </sheetData>
@@ -15360,26 +15360,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>230.75</v>
+        <v>233.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>43.5</v>
+        <v>45.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>11</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>285.25</v>
+        <v>290.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>592.2</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
     </row>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>103.25</v>
+        <v>107</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15399,7 +15399,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>118.25</v>
+        <v>122</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15.5</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.9%</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>126.75</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -15585,7 +15585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15609,7 +15609,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 28 commande(s)</t>
+          <t>Épics créées ce mois — 29 commande(s)</t>
         </is>
       </c>
     </row>
@@ -15664,22 +15664,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -15699,32 +15699,32 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33694</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -15744,32 +15744,32 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00169321</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>1500</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33662</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33656</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>TARARE</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -15789,11 +15789,11 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00169254</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1700</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="8">
@@ -15844,22 +15844,22 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33662</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33656</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>TARARE</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00169254</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
@@ -15889,22 +15889,22 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33694</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -15924,32 +15924,32 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00169321</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -15969,32 +15969,32 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169558</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>5050</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -16014,32 +16014,32 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00169558</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>1950</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -16059,32 +16059,32 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>2035</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -16104,32 +16104,32 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>1700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-33980</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-33976</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE SAINT PRIEST</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -16149,32 +16149,32 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170407</t>
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>3370</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34054</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34045</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -16194,32 +16194,32 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>00170461</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>4250</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -16239,11 +16239,11 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>3000</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="18">
@@ -16294,22 +16294,22 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -16329,32 +16329,32 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>3535</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33980</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33976</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PRIEST</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -16374,42 +16374,42 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00170407</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>500</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-34054</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-34045</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -16419,32 +16419,32 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00170461</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>1350</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -16464,11 +16464,11 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="23">
@@ -16519,22 +16519,22 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>2300</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -16599,32 +16599,32 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
-        <v>6655</v>
+        <v>755</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -16644,32 +16644,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>1890</v>
+        <v>12429</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -16689,32 +16689,32 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>895</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -16727,35 +16727,39 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr"/>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>2625</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -16775,32 +16779,32 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>2200</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -16820,32 +16824,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>12429</v>
+        <v>895</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -16858,90 +16862,110 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G31" s="15" t="inlineStr"/>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>755</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-33724</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33720</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>00169462</t>
+        </is>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-33817</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-33813</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H33" s="15" t="inlineStr">
         <is>
           <t>00169865</t>
         </is>
       </c>
-      <c r="I32" s="27" t="n">
+      <c r="I33" s="26" t="n">
         <v>1095.5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="inlineStr">
-        <is>
-          <t>28 commande(s)</t>
-        </is>
-      </c>
-      <c r="I33" s="25" t="n">
-        <v>77420</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B34" s="18" t="n"/>
@@ -16952,17 +16976,17 @@
       <c r="G34" s="18" t="n"/>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>12 commande(s)</t>
+          <t>29 commande(s)</t>
         </is>
       </c>
       <c r="I34" s="25" t="n">
-        <v>35034</v>
+        <v>77420</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B35" s="18" t="n"/>
@@ -16973,10 +16997,31 @@
       <c r="G35" s="18" t="n"/>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>16 commande(s)</t>
+          <t>12 commande(s)</t>
         </is>
       </c>
       <c r="I35" s="25" t="n">
+        <v>35034</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>17 commande(s)</t>
+        </is>
+      </c>
+      <c r="I36" s="25" t="n">
         <v>42385</v>
       </c>
     </row>
